--- a/salidas/empresas/APD.xlsx
+++ b/salidas/empresas/APD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.87707138061523</v>
+        <v>35.87705993652344</v>
       </c>
       <c r="C3" t="n">
         <v>59.35245132446289</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76356506347656</v>
+        <v>37.76356887817383</v>
       </c>
       <c r="C4" t="n">
         <v>62.15541076660156</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.51110458374023</v>
+        <v>38.51108932495117</v>
       </c>
       <c r="C5" t="n">
         <v>63.3857536315918</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>36.44839096069336</v>
+        <v>36.44838333129883</v>
       </c>
       <c r="C6" t="n">
         <v>59.99074935913086</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>36.12398910522461</v>
+        <v>36.12399673461914</v>
       </c>
       <c r="C7" t="n">
         <v>59.13043594360352</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>36.12963104248047</v>
+        <v>36.129638671875</v>
       </c>
       <c r="C8" t="n">
         <v>59.13968658447266</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>37.69816589355469</v>
+        <v>37.69815444946289</v>
       </c>
       <c r="C10" t="n">
         <v>61.39685440063477</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>39.57256698608398</v>
+        <v>39.57255935668945</v>
       </c>
       <c r="C11" t="n">
         <v>64.4495849609375</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.27152633666992</v>
+        <v>39.27153396606445</v>
       </c>
       <c r="C12" t="n">
         <v>63.95929718017578</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.10863494873047</v>
+        <v>40.1086311340332</v>
       </c>
       <c r="C13" t="n">
         <v>65.01387786865234</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.60828018188477</v>
+        <v>42.60829925537109</v>
       </c>
       <c r="C14" t="n">
         <v>69.06568145751953</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.69390106201172</v>
+        <v>42.69388961791992</v>
       </c>
       <c r="C15" t="n">
         <v>69.20443725585938</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.42668151855469</v>
+        <v>42.42669677734375</v>
       </c>
       <c r="C16" t="n">
         <v>68.41812896728516</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>43.88375854492188</v>
+        <v>43.88375091552734</v>
       </c>
       <c r="C17" t="n">
         <v>70.76780700683594</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>44.73847961425781</v>
+        <v>44.73848342895508</v>
       </c>
       <c r="C18" t="n">
         <v>72.14616394042969</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>46.31968688964844</v>
+        <v>46.3196907043457</v>
       </c>
       <c r="C19" t="n">
         <v>74.34782409667969</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>49.77766418457031</v>
+        <v>49.77768325805664</v>
       </c>
       <c r="C20" t="n">
         <v>79.89823913574219</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>56.61540603637695</v>
+        <v>56.61538696289062</v>
       </c>
       <c r="C23" t="n">
         <v>90.51803588867188</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.30392074584961</v>
+        <v>57.30393600463867</v>
       </c>
       <c r="C24" t="n">
         <v>91.61887359619141</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>57.28255462646484</v>
+        <v>57.28253936767578</v>
       </c>
       <c r="C25" t="n">
         <v>91.23959350585938</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>52.07874298095703</v>
+        <v>52.07876586914062</v>
       </c>
       <c r="C26" t="n">
         <v>82.95097351074219</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>53.04284286499023</v>
+        <v>53.0428352355957</v>
       </c>
       <c r="C27" t="n">
         <v>84.48658752441406</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>53.68692398071289</v>
+        <v>53.68689346313477</v>
       </c>
       <c r="C28" t="n">
         <v>85.10638427734375</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>59.47578048706055</v>
+        <v>59.47577285766602</v>
       </c>
       <c r="C30" t="n">
         <v>94.28307342529297</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>55.80945587158203</v>
+        <v>55.8094367980957</v>
       </c>
       <c r="C32" t="n">
         <v>88.07585906982422</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>53.83988571166992</v>
+        <v>53.83989715576172</v>
       </c>
       <c r="C33" t="n">
         <v>84.96762084960938</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>40.39573669433594</v>
+        <v>40.39574813842773</v>
       </c>
       <c r="C34" t="n">
         <v>63.35800170898438</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>34.28536224365234</v>
+        <v>34.28536605834961</v>
       </c>
       <c r="C35" t="n">
         <v>53.77428436279297</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>28.16908073425293</v>
+        <v>28.16909217834473</v>
       </c>
       <c r="C36" t="n">
         <v>44.18131256103516</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>29.92419815063477</v>
+        <v>29.92421722412109</v>
       </c>
       <c r="C37" t="n">
         <v>46.50323867797852</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>29.94206619262695</v>
+        <v>29.94206809997559</v>
       </c>
       <c r="C38" t="n">
         <v>46.53099060058594</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>27.53121757507324</v>
+        <v>27.53121185302734</v>
       </c>
       <c r="C39" t="n">
         <v>42.78445816040039</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.74228668212891</v>
+        <v>33.74229431152344</v>
       </c>
       <c r="C40" t="n">
         <v>52.03515243530273</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>39.53096389770508</v>
+        <v>39.53095245361328</v>
       </c>
       <c r="C41" t="n">
         <v>60.96207046508789</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>38.8591194152832</v>
+        <v>38.85911178588867</v>
       </c>
       <c r="C42" t="n">
         <v>59.92599487304688</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>39.01445770263672</v>
+        <v>39.01444625854492</v>
       </c>
       <c r="C43" t="n">
         <v>59.7502326965332</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>45.06081390380859</v>
+        <v>45.06080627441406</v>
       </c>
       <c r="C44" t="n">
         <v>69.01017761230469</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>45.32056045532227</v>
+        <v>45.32054901123047</v>
       </c>
       <c r="C45" t="n">
         <v>69.407958984375</v>
@@ -1330,7 +1342,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>46.8574333190918</v>
+        <v>46.85743713378906</v>
       </c>
       <c r="C47" t="n">
         <v>71.35060119628906</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>50.38100433349609</v>
+        <v>50.38098907470703</v>
       </c>
       <c r="C48" t="n">
         <v>76.71600341796875</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>49.51444244384766</v>
+        <v>49.51443099975586</v>
       </c>
       <c r="C49" t="n">
         <v>74.98612213134766</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>46.39917373657227</v>
+        <v>46.399169921875</v>
       </c>
       <c r="C50" t="n">
         <v>70.26827239990234</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.89118957519531</v>
+        <v>41.89119720458984</v>
       </c>
       <c r="C51" t="n">
         <v>63.44125747680664</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>45.47126007080078</v>
+        <v>45.47126388549805</v>
       </c>
       <c r="C52" t="n">
         <v>68.40888214111328</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>47.21138763427734</v>
+        <v>47.21140289306641</v>
       </c>
       <c r="C53" t="n">
         <v>71.02682495117188</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>42.46442413330078</v>
+        <v>42.46444702148438</v>
       </c>
       <c r="C54" t="n">
         <v>63.88529205322266</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.14131164550781</v>
+        <v>40.14129257202148</v>
       </c>
       <c r="C55" t="n">
         <v>59.9537467956543</v>
@@ -1580,7 +1592,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>45.85190963745117</v>
+        <v>45.85188293457031</v>
       </c>
       <c r="C57" t="n">
         <v>68.48288726806641</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>51.59722518920898</v>
+        <v>51.59723281860352</v>
       </c>
       <c r="C58" t="n">
         <v>76.61424255371094</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>52.93667602539062</v>
+        <v>52.93669509887695</v>
       </c>
       <c r="C59" t="n">
         <v>78.60314178466797</v>
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1709,11 +1721,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>56.9681510925293</v>
+        <v>56.96817016601562</v>
       </c>
       <c r="C61" t="n">
         <v>84.13506317138672</v>
@@ -1738,11 +1750,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>54.65061569213867</v>
+        <v>54.65060424804688</v>
       </c>
       <c r="C62" t="n">
         <v>80.71230316162109</v>
@@ -1767,11 +1779,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>57.6258544921875</v>
+        <v>57.62583160400391</v>
       </c>
       <c r="C63" t="n">
         <v>85.10638427734375</v>
@@ -1796,11 +1808,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>56.85109710693359</v>
+        <v>56.85111618041992</v>
       </c>
       <c r="C64" t="n">
         <v>83.42276000976562</v>
@@ -1825,11 +1837,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>60.21752166748047</v>
+        <v>60.21749877929688</v>
       </c>
       <c r="C65" t="n">
         <v>88.36262512207031</v>
@@ -1854,11 +1866,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>59.94644927978516</v>
+        <v>59.94644546508789</v>
       </c>
       <c r="C66" t="n">
         <v>87.96484375</v>
@@ -1883,7 +1895,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1912,11 +1924,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.28118133544922</v>
+        <v>56.28118896484375</v>
       </c>
       <c r="C68" t="n">
         <v>82.08140563964844</v>
@@ -1941,11 +1953,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>51.92990493774414</v>
+        <v>51.92989349365234</v>
       </c>
       <c r="C69" t="n">
         <v>75.73542785644531</v>
@@ -1970,11 +1982,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>48.79953384399414</v>
+        <v>48.799560546875</v>
       </c>
       <c r="C70" t="n">
         <v>70.64755249023438</v>
@@ -1999,11 +2011,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>55.04244613647461</v>
+        <v>55.04245758056641</v>
       </c>
       <c r="C71" t="n">
         <v>79.68547821044922</v>
@@ -2028,11 +2040,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>53.51528167724609</v>
+        <v>53.5152702331543</v>
       </c>
       <c r="C72" t="n">
         <v>77.47456359863281</v>
@@ -2057,11 +2069,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>54.80950164794922</v>
+        <v>54.80949783325195</v>
       </c>
       <c r="C73" t="n">
         <v>78.80666351318359</v>
@@ -2086,11 +2098,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>56.63669967651367</v>
+        <v>56.6367073059082</v>
       </c>
       <c r="C74" t="n">
         <v>81.43386077880859</v>
@@ -2115,11 +2127,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>58.05858993530273</v>
+        <v>58.05860137939453</v>
       </c>
       <c r="C75" t="n">
         <v>83.47826385498047</v>
@@ -2144,11 +2156,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>59.47996520996094</v>
+        <v>59.47995758056641</v>
       </c>
       <c r="C76" t="n">
         <v>84.92137145996094</v>
@@ -2173,11 +2185,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>55.39153289794922</v>
+        <v>55.39152145385742</v>
       </c>
       <c r="C77" t="n">
         <v>79.08418273925781</v>
@@ -2202,11 +2214,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>51.21237564086914</v>
+        <v>51.21237182617188</v>
       </c>
       <c r="C78" t="n">
         <v>73.11748504638672</v>
@@ -2231,7 +2243,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2260,11 +2272,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>52.54862976074219</v>
+        <v>52.54864883422852</v>
       </c>
       <c r="C80" t="n">
         <v>74.40332794189453</v>
@@ -2289,11 +2301,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>53.95333862304688</v>
+        <v>53.95335006713867</v>
       </c>
       <c r="C81" t="n">
         <v>76.39222717285156</v>
@@ -2318,11 +2330,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>54.45070648193359</v>
+        <v>54.45068359375</v>
       </c>
       <c r="C82" t="n">
         <v>76.50323486328125</v>
@@ -2347,11 +2359,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>51.04669952392578</v>
+        <v>51.04670333862305</v>
       </c>
       <c r="C83" t="n">
         <v>71.72062683105469</v>
@@ -2376,7 +2388,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2405,11 +2417,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>55.7404670715332</v>
+        <v>55.740478515625</v>
       </c>
       <c r="C85" t="n">
         <v>77.72432708740234</v>
@@ -2434,11 +2446,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>58.00273132324219</v>
+        <v>58.00272369384766</v>
       </c>
       <c r="C86" t="n">
         <v>80.87881469726562</v>
@@ -2463,11 +2475,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.27959442138672</v>
+        <v>57.27962112426758</v>
       </c>
       <c r="C87" t="n">
         <v>79.87049102783203</v>
@@ -2492,11 +2504,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.26762390136719</v>
+        <v>58.26760864257812</v>
       </c>
       <c r="C88" t="n">
         <v>80.592041015625</v>
@@ -2521,11 +2533,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>58.16059112548828</v>
+        <v>58.16060256958008</v>
       </c>
       <c r="C89" t="n">
         <v>80.44403076171875</v>
@@ -2550,11 +2562,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>63.143310546875</v>
+        <v>63.14330291748047</v>
       </c>
       <c r="C90" t="n">
         <v>87.33580017089844</v>
@@ -2579,11 +2591,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.69958877563477</v>
+        <v>61.69956207275391</v>
       </c>
       <c r="C91" t="n">
         <v>84.70860290527344</v>
@@ -2608,7 +2620,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2637,11 +2649,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>68.82160186767578</v>
+        <v>68.82157897949219</v>
       </c>
       <c r="C93" t="n">
         <v>94.48658752441406</v>
@@ -2666,7 +2678,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2695,7 +2707,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2724,11 +2736,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>73.806640625</v>
+        <v>73.80663299560547</v>
       </c>
       <c r="C96" t="n">
         <v>100.6753005981445</v>
@@ -2753,11 +2765,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>76.28477478027344</v>
+        <v>76.28478240966797</v>
       </c>
       <c r="C97" t="n">
         <v>103.4042587280273</v>
@@ -2782,11 +2794,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>71.75325012207031</v>
+        <v>71.75327301025391</v>
       </c>
       <c r="C98" t="n">
         <v>97.26179504394531</v>
@@ -2811,7 +2823,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2840,11 +2852,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>81.77097320556641</v>
+        <v>81.77101898193359</v>
       </c>
       <c r="C100" t="n">
         <v>110.1202621459961</v>
@@ -2869,11 +2881,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>80.72690582275391</v>
+        <v>80.72688293457031</v>
       </c>
       <c r="C101" t="n">
         <v>108.7141571044922</v>
@@ -2898,11 +2910,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>82.40984344482422</v>
+        <v>82.40983581542969</v>
       </c>
       <c r="C102" t="n">
         <v>110.9805755615234</v>
@@ -2927,11 +2939,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>88.88295745849609</v>
+        <v>88.8829345703125</v>
       </c>
       <c r="C103" t="n">
         <v>118.982421875</v>
@@ -2956,11 +2968,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>91.18412780761719</v>
+        <v>91.18415832519531</v>
       </c>
       <c r="C104" t="n">
         <v>122.0629043579102</v>
@@ -2985,11 +2997,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>92.05487060546875</v>
+        <v>92.05487823486328</v>
       </c>
       <c r="C105" t="n">
         <v>123.2284927368164</v>
@@ -3014,11 +3026,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>90.47792816162109</v>
+        <v>90.47791290283203</v>
       </c>
       <c r="C106" t="n">
         <v>120.4255294799805</v>
@@ -3043,7 +3055,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3072,11 +3084,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>99.96498870849609</v>
+        <v>99.96495819091797</v>
       </c>
       <c r="C108" t="n">
         <v>133.052734375</v>
@@ -3101,11 +3113,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>100.7660369873047</v>
+        <v>100.7660293579102</v>
       </c>
       <c r="C109" t="n">
         <v>133.4227600097656</v>
@@ -3130,11 +3142,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>101.7301330566406</v>
+        <v>101.7301788330078</v>
       </c>
       <c r="C110" t="n">
         <v>134.6993560791016</v>
@@ -3159,7 +3171,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3188,11 +3200,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>106.2549591064453</v>
+        <v>106.2549438476562</v>
       </c>
       <c r="C112" t="n">
         <v>139.9444885253906</v>
@@ -3217,11 +3229,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>100.7413330078125</v>
+        <v>100.7413101196289</v>
       </c>
       <c r="C113" t="n">
         <v>132.6826934814453</v>
@@ -3246,11 +3258,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>103.0802154541016</v>
+        <v>103.0802307128906</v>
       </c>
       <c r="C114" t="n">
         <v>135.76318359375</v>
@@ -3275,7 +3287,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3304,11 +3316,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>100.6690521240234</v>
+        <v>100.669059753418</v>
       </c>
       <c r="C116" t="n">
         <v>131.8316345214844</v>
@@ -3333,11 +3345,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>98.56401824951172</v>
+        <v>98.56400299072266</v>
       </c>
       <c r="C117" t="n">
         <v>129.0749359130859</v>
@@ -3362,11 +3374,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>90.70912933349609</v>
+        <v>90.70913696289062</v>
       </c>
       <c r="C118" t="n">
         <v>118.0203552246094</v>
@@ -3391,11 +3403,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>98.81449890136719</v>
+        <v>98.81451416015625</v>
       </c>
       <c r="C119" t="n">
         <v>128.5661468505859</v>
@@ -3420,11 +3432,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>97.32852172851562</v>
+        <v>97.32851409912109</v>
       </c>
       <c r="C120" t="n">
         <v>126.6327438354492</v>
@@ -3449,11 +3461,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>93.07395172119141</v>
+        <v>93.07391357421875</v>
       </c>
       <c r="C121" t="n">
         <v>120.3607788085938</v>
@@ -3478,11 +3490,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>90.64177703857422</v>
+        <v>90.64179229736328</v>
       </c>
       <c r="C122" t="n">
         <v>117.2155380249023</v>
@@ -3507,7 +3519,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3536,11 +3548,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>103.6605758666992</v>
+        <v>103.6605453491211</v>
       </c>
       <c r="C124" t="n">
         <v>133.2562408447266</v>
@@ -3565,11 +3577,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>104.9846725463867</v>
+        <v>104.9846649169922</v>
       </c>
       <c r="C125" t="n">
         <v>134.9583740234375</v>
@@ -3594,11 +3606,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>102.6459274291992</v>
+        <v>102.6459121704102</v>
       </c>
       <c r="C126" t="n">
         <v>131.9518890380859</v>
@@ -3623,11 +3635,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>102.8611755371094</v>
+        <v>102.8611679077148</v>
       </c>
       <c r="C127" t="n">
         <v>131.3968505859375</v>
@@ -3652,11 +3664,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>108.2055587768555</v>
+        <v>108.2055435180664</v>
       </c>
       <c r="C128" t="n">
         <v>138.2238616943359</v>
@@ -3681,11 +3693,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>112.6954193115234</v>
+        <v>112.6953964233398</v>
       </c>
       <c r="C129" t="n">
         <v>143.9592895507812</v>
@@ -3710,11 +3722,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>108.8717803955078</v>
+        <v>108.8717956542969</v>
       </c>
       <c r="C130" t="n">
         <v>139.0749359130859</v>
@@ -3739,11 +3751,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>105.1048202514648</v>
+        <v>105.1048126220703</v>
       </c>
       <c r="C131" t="n">
         <v>133.4199981689453</v>
@@ -3768,11 +3780,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>113.801887512207</v>
+        <v>113.801872253418</v>
       </c>
       <c r="C132" t="n">
         <v>144.4600067138672</v>
@@ -3797,11 +3809,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>113.9731292724609</v>
+        <v>113.9730987548828</v>
       </c>
       <c r="C133" t="n">
         <v>143.8200073242188</v>
@@ -3826,11 +3838,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>110.7556686401367</v>
+        <v>110.7556457519531</v>
       </c>
       <c r="C134" t="n">
         <v>139.7599945068359</v>
@@ -3855,11 +3867,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>111.3183364868164</v>
+        <v>111.3183670043945</v>
       </c>
       <c r="C135" t="n">
         <v>140.4700012207031</v>
@@ -3884,11 +3896,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>107.9631958007812</v>
+        <v>107.9631805419922</v>
       </c>
       <c r="C136" t="n">
         <v>135.2899932861328</v>
@@ -3913,7 +3925,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3942,11 +3954,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>114.9617919921875</v>
+        <v>114.9617691040039</v>
       </c>
       <c r="C138" t="n">
         <v>144.0599975585938</v>
@@ -3971,11 +3983,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>114.91748046875</v>
+        <v>114.9174499511719</v>
       </c>
       <c r="C139" t="n">
         <v>143.0599975585938</v>
@@ -4000,11 +4012,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>114.1864700317383</v>
+        <v>114.1865005493164</v>
       </c>
       <c r="C140" t="n">
         <v>142.1499938964844</v>
@@ -4029,11 +4041,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>116.7730331420898</v>
+        <v>116.7730560302734</v>
       </c>
       <c r="C141" t="n">
         <v>145.3699951171875</v>
@@ -4058,11 +4070,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>121.4722747802734</v>
+        <v>121.4722900390625</v>
       </c>
       <c r="C142" t="n">
         <v>151.2200012207031</v>
@@ -4087,11 +4099,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>128.86572265625</v>
+        <v>128.8657379150391</v>
       </c>
       <c r="C143" t="n">
         <v>159.4299926757812</v>
@@ -4116,11 +4128,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>131.7836608886719</v>
+        <v>131.7836303710938</v>
       </c>
       <c r="C144" t="n">
         <v>163.0399932861328</v>
@@ -4145,11 +4157,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>133.3941192626953</v>
+        <v>133.3940734863281</v>
       </c>
       <c r="C145" t="n">
         <v>164.0800018310547</v>
@@ -4174,11 +4186,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>136.8817443847656</v>
+        <v>136.8817901611328</v>
       </c>
       <c r="C146" t="n">
         <v>168.3699951171875</v>
@@ -4203,11 +4215,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>130.7193603515625</v>
+        <v>130.7193450927734</v>
       </c>
       <c r="C147" t="n">
         <v>160.7899932861328</v>
@@ -4232,11 +4244,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>130.1938934326172</v>
+        <v>130.1938781738281</v>
       </c>
       <c r="C148" t="n">
         <v>159.0299987792969</v>
@@ -4261,11 +4273,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>132.8627624511719</v>
+        <v>132.8628082275391</v>
       </c>
       <c r="C149" t="n">
         <v>162.2899932861328</v>
@@ -4290,11 +4302,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>132.1423645019531</v>
+        <v>132.1423187255859</v>
       </c>
       <c r="C150" t="n">
         <v>161.4100036621094</v>
@@ -4319,11 +4331,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>128.3974609375</v>
+        <v>128.3974914550781</v>
       </c>
       <c r="C151" t="n">
         <v>155.7299957275391</v>
@@ -4348,7 +4360,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4377,11 +4389,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>137.1040191650391</v>
+        <v>137.1040344238281</v>
       </c>
       <c r="C153" t="n">
         <v>166.2899932861328</v>
@@ -4406,11 +4418,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>138.6355743408203</v>
+        <v>138.6355895996094</v>
       </c>
       <c r="C154" t="n">
         <v>167.0500030517578</v>
@@ -4435,11 +4447,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>128.0957946777344</v>
+        <v>128.0958099365234</v>
       </c>
       <c r="C155" t="n">
         <v>154.3500061035156</v>
@@ -4464,11 +4476,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>133.5067749023438</v>
+        <v>133.5067596435547</v>
       </c>
       <c r="C156" t="n">
         <v>160.8699951171875</v>
@@ -4493,11 +4505,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>133.7417449951172</v>
+        <v>133.7417297363281</v>
       </c>
       <c r="C157" t="n">
         <v>160.0500030517578</v>
@@ -4522,11 +4534,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>137.3683319091797</v>
+        <v>137.3683929443359</v>
       </c>
       <c r="C158" t="n">
         <v>164.3899993896484</v>
@@ -4551,11 +4563,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>151.3984680175781</v>
+        <v>151.3984985351562</v>
       </c>
       <c r="C159" t="n">
         <v>181.1799926757812</v>
@@ -4580,7 +4592,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4609,11 +4621,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>173.0185546875</v>
+        <v>173.0186004638672</v>
       </c>
       <c r="C161" t="n">
         <v>205.7899932861328</v>
@@ -4638,11 +4650,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>171.1689910888672</v>
+        <v>171.1689605712891</v>
       </c>
       <c r="C162" t="n">
         <v>203.5899963378906</v>
@@ -4667,11 +4679,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>191.3142700195312</v>
+        <v>191.3142547607422</v>
       </c>
       <c r="C163" t="n">
         <v>226.3699951171875</v>
@@ -4696,11 +4708,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>192.9200134277344</v>
+        <v>192.9199981689453</v>
       </c>
       <c r="C164" t="n">
         <v>228.2700042724609</v>
@@ -4725,11 +4737,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>190.9339599609375</v>
+        <v>190.9339141845703</v>
       </c>
       <c r="C165" t="n">
         <v>225.9199981689453</v>
@@ -4754,11 +4766,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>188.4918060302734</v>
+        <v>188.4917755126953</v>
       </c>
       <c r="C166" t="n">
         <v>221.8600006103516</v>
@@ -4783,7 +4795,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4812,11 +4824,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>200.7854156494141</v>
+        <v>200.7854614257812</v>
       </c>
       <c r="C168" t="n">
         <v>236.3300018310547</v>
@@ -4841,11 +4853,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>200.6359710693359</v>
+        <v>200.635986328125</v>
       </c>
       <c r="C169" t="n">
         <v>234.9900054931641</v>
@@ -4870,7 +4882,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4899,7 +4911,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4928,11 +4940,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>171.5412902832031</v>
+        <v>171.541259765625</v>
       </c>
       <c r="C172" t="n">
         <v>199.6100006103516</v>
@@ -4957,11 +4969,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>193.8594360351562</v>
+        <v>193.8594818115234</v>
       </c>
       <c r="C173" t="n">
         <v>225.5800018310547</v>
@@ -4986,11 +4998,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>207.6697387695312</v>
+        <v>207.6697082519531</v>
       </c>
       <c r="C174" t="n">
         <v>241.6499938964844</v>
@@ -5015,11 +5027,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>208.6782989501953</v>
+        <v>208.6783142089844</v>
       </c>
       <c r="C175" t="n">
         <v>241.4600067138672</v>
@@ -5044,11 +5056,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>247.7158508300781</v>
+        <v>247.7158966064453</v>
       </c>
       <c r="C176" t="n">
         <v>286.6300048828125</v>
@@ -5073,11 +5085,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>252.5814971923828</v>
+        <v>252.5815124511719</v>
       </c>
       <c r="C177" t="n">
         <v>292.260009765625</v>
@@ -5102,11 +5114,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>258.6004028320312</v>
+        <v>258.6004638671875</v>
       </c>
       <c r="C178" t="n">
         <v>297.8599853515625</v>
@@ -5131,11 +5143,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>239.8300018310547</v>
+        <v>239.830078125</v>
       </c>
       <c r="C179" t="n">
         <v>276.239990234375</v>
@@ -5160,7 +5172,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5189,11 +5201,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>238.3864135742188</v>
+        <v>238.3864440917969</v>
       </c>
       <c r="C181" t="n">
         <v>273.2200012207031</v>
@@ -5218,11 +5230,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>232.7500305175781</v>
+        <v>232.7500152587891</v>
       </c>
       <c r="C182" t="n">
         <v>266.760009765625</v>
@@ -5247,11 +5259,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>223.0303039550781</v>
+        <v>223.0302734375</v>
       </c>
       <c r="C183" t="n">
         <v>255.6199951171875</v>
@@ -5276,7 +5288,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5305,11 +5317,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>253.0439605712891</v>
+        <v>253.0439147949219</v>
       </c>
       <c r="C185" t="n">
         <v>288.4800109863281</v>
@@ -5334,11 +5346,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>262.8506164550781</v>
+        <v>262.8505554199219</v>
       </c>
       <c r="C186" t="n">
         <v>299.6600036621094</v>
@@ -5363,7 +5375,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5392,11 +5404,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>256.6159057617188</v>
+        <v>256.6159362792969</v>
       </c>
       <c r="C188" t="n">
         <v>291.0299987792969</v>
@@ -5421,11 +5433,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>237.6406707763672</v>
+        <v>237.6407012939453</v>
       </c>
       <c r="C189" t="n">
         <v>269.510009765625</v>
@@ -5450,11 +5462,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>227.1344604492188</v>
+        <v>227.1344451904297</v>
       </c>
       <c r="C190" t="n">
         <v>256.1099853515625</v>
@@ -5479,7 +5491,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5508,11 +5520,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>254.9199371337891</v>
+        <v>254.9198455810547</v>
       </c>
       <c r="C192" t="n">
         <v>287.4400024414062</v>
@@ -5537,11 +5549,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>271.1754150390625</v>
+        <v>271.1754455566406</v>
       </c>
       <c r="C193" t="n">
         <v>304.260009765625</v>
@@ -5566,11 +5578,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>251.4428253173828</v>
+        <v>251.44287109375</v>
       </c>
       <c r="C194" t="n">
         <v>282.1199951171875</v>
@@ -5595,7 +5607,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5624,11 +5636,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>224.1698455810547</v>
+        <v>224.1698303222656</v>
       </c>
       <c r="C196" t="n">
         <v>249.9100036621094</v>
@@ -5653,7 +5665,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5682,7 +5694,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5711,7 +5723,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5740,11 +5752,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>224.1564025878906</v>
+        <v>224.1564331054688</v>
       </c>
       <c r="C200" t="n">
         <v>248.2299957275391</v>
@@ -5769,7 +5781,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5798,7 +5810,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5827,11 +5839,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>227.7076568603516</v>
+        <v>227.7076721191406</v>
       </c>
       <c r="C203" t="n">
         <v>250.3999938964844</v>
@@ -5856,11 +5868,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>282.0519714355469</v>
+        <v>282.0519104003906</v>
       </c>
       <c r="C204" t="n">
         <v>310.1600036621094</v>
@@ -5885,7 +5897,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5914,11 +5926,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>292.9881286621094</v>
+        <v>292.9881591796875</v>
       </c>
       <c r="C206" t="n">
         <v>320.510009765625</v>
@@ -5943,11 +5955,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>261.4232482910156</v>
+        <v>261.4232177734375</v>
       </c>
       <c r="C207" t="n">
         <v>285.9800109863281</v>
@@ -5972,7 +5984,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -6001,11 +6013,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>270.7776794433594</v>
+        <v>270.7777099609375</v>
       </c>
       <c r="C209" t="n">
         <v>294.3599853515625</v>
@@ -6030,11 +6042,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>247.5781402587891</v>
+        <v>247.5782165527344</v>
       </c>
       <c r="C210" t="n">
         <v>269.1400146484375</v>
@@ -6059,11 +6071,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>277.1791687011719</v>
+        <v>277.17919921875</v>
       </c>
       <c r="C211" t="n">
         <v>299.5299987792969</v>
@@ -6088,7 +6100,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6117,7 +6129,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6146,11 +6158,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>263.8624572753906</v>
+        <v>263.8624267578125</v>
       </c>
       <c r="C214" t="n">
         <v>283.3999938964844</v>
@@ -6175,7 +6187,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6204,7 +6216,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6233,7 +6245,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6262,7 +6274,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6291,11 +6303,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>219.3047943115234</v>
+        <v>219.3047790527344</v>
       </c>
       <c r="C219" t="n">
         <v>234.0399932861328</v>
@@ -6320,7 +6332,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6349,7 +6361,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6378,11 +6390,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>251.7414398193359</v>
+        <v>251.7414703369141</v>
       </c>
       <c r="C222" t="n">
         <v>266.7000122070312</v>
@@ -6407,11 +6419,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>243.5765838623047</v>
+        <v>243.5765686035156</v>
       </c>
       <c r="C223" t="n">
         <v>258.0499877929688</v>
@@ -6436,11 +6448,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>250.7713165283203</v>
+        <v>250.7713470458984</v>
       </c>
       <c r="C224" t="n">
         <v>263.8500061035156</v>
@@ -6465,11 +6477,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>265.0278625488281</v>
+        <v>265.02783203125</v>
       </c>
       <c r="C225" t="n">
         <v>278.8500061035156</v>
@@ -6494,7 +6506,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6523,11 +6535,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>296.9025573730469</v>
+        <v>296.9025268554688</v>
       </c>
       <c r="C227" t="n">
         <v>310.5299987792969</v>
@@ -6552,11 +6564,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>319.6580200195312</v>
+        <v>319.6580810546875</v>
       </c>
       <c r="C228" t="n">
         <v>334.3299865722656</v>
@@ -6581,7 +6593,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6610,7 +6622,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6639,11 +6651,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>304.1318969726562</v>
+        <v>304.1318664550781</v>
       </c>
       <c r="C231" t="n">
         <v>316.1499938964844</v>
@@ -6668,7 +6680,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6697,7 +6709,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6726,7 +6738,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6755,7 +6767,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6784,11 +6796,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>280.4071655273438</v>
+        <v>280.4071960449219</v>
       </c>
       <c r="C236" t="n">
         <v>287.8800048828125</v>
@@ -6813,7 +6825,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6842,11 +6854,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>265.6407165527344</v>
+        <v>265.6406555175781</v>
       </c>
       <c r="C238" t="n">
         <v>272.7200012207031</v>
@@ -6871,7 +6883,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6900,11 +6912,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>255.9535675048828</v>
+        <v>255.9535522460938</v>
       </c>
       <c r="C240" t="n">
         <v>261.0499877929688</v>
@@ -6927,11 +6939,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>242.1974792480469</v>
+        <v>242.1974945068359</v>
       </c>
       <c r="C241" t="n">
         <v>247.0200042724609</v>
@@ -6954,7 +6966,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6981,7 +6993,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7008,7 +7020,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7035,7 +7047,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7064,7 +7076,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7093,7 +7105,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7122,7 +7134,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7176,17 +7188,17 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>286.9700012207031</v>
+        <v>284.489990234375</v>
       </c>
       <c r="C250" t="n">
-        <v>286.9700012207031</v>
+        <v>284.489990234375</v>
       </c>
       <c r="D250" t="n">
-        <v>19187700</v>
+        <v>20234100</v>
       </c>
       <c r="E250" t="n">
         <v>-0.21</v>
@@ -7196,10 +7208,10 @@
         <v>222685530</v>
       </c>
       <c r="H250" t="n">
-        <v>63904066815.93292</v>
+        <v>63351804255.03662</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08616500587173311</v>
+        <v>0.0908640089906156</v>
       </c>
     </row>
   </sheetData>
@@ -7231,75 +7243,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7335,13 +7347,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40204</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7377,13 +7389,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40294</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7419,13 +7431,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7461,13 +7473,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7494,7 +7506,7 @@
       <c r="I6" t="n">
         <v>2.72895467160037</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K6" t="n">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40204</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>3.506012950971323</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40294</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>3.681776133209991</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40385</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>4.27382053654024</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>4.384828862164662</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40569</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>4.449583718778909</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40569</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40659</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>4.662349676225717</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40659</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>4.967622571692877</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>5.208140610545792</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>5.143385753931545</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>5.13413506012951</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>5.837187789084181</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>5.041628122109158</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>5.180388529139686</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>5.180388529139686</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>4.347826086956522</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41604</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>4.338575393154487</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41604</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41668</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>4.375578168362628</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41668</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>4.320074005550417</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>4.412580943570768</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41967</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>4.264569842738206</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41967</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>4.403330249768733</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>4.412580943570768</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>4.421831637372803</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>5.43940795559667</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>5.596669750231268</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>2.358926919518964</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>2.469935245143386</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42695</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>2.808325624421832</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42695</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>2.633459759481962</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>14.34086031452359</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>13.33</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43055</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>13.66</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43055</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>12.99</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>5.18</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>6.869999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>6.789999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>7.659999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>7.67</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>7.72</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>7.94</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>8.510000000000002</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>8.76</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>8.57</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>8.49</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>8.52</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>8.5</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44417</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>8.889999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44417</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44518</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>9.43</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44518</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>9.780000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>10.03</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>10.25</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>10.14</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>10.19</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>9.83</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45246</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>10.33</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45246</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>10.49</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>11.09</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>11.55</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>17.18</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>17.22</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>6.879999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>6.95</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>-1.77</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>-1.5</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>9.459999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10576,7 +10588,7 @@
       <c r="I73" t="n">
         <v>-0.21</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K73" t="n">
@@ -10613,52 +10625,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40014</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="C2" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40137</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40142</v>
       </c>
       <c r="C3" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40197</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40204</v>
       </c>
       <c r="C4" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40287</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40294</v>
       </c>
       <c r="C5" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40378</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40385</v>
       </c>
       <c r="C6" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40497</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="C7" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40561</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40569</v>
       </c>
       <c r="C8" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40658</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40659</v>
       </c>
       <c r="C9" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40742</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C10" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="C11" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="C12" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C13" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C14" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="C16" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C17" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41604</v>
       </c>
       <c r="C19" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41668</v>
       </c>
       <c r="C20" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C21" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C22" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41967</v>
       </c>
       <c r="C23" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="C24" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C25" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="C27" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="C28" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C29" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C30" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42695</v>
       </c>
       <c r="C31" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="C32" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C34" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43055</v>
       </c>
       <c r="C35" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="C36" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="C39" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="C40" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C42" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="C43" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="C44" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="C45" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C46" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="C47" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="C48" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="C49" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44417</v>
       </c>
       <c r="C50" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44518</v>
       </c>
       <c r="C51" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="C52" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C53" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="C55" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C56" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="C57" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45246</v>
       </c>
       <c r="C59" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="C60" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C61" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="C63" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C64" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C66" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="C67" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C68" t="n">
@@ -12799,10 +12811,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12831,10 +12843,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C70" t="n">
@@ -12881,12 +12893,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/APD.xlsx
+++ b/salidas/empresas/APD.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>34.49589157104492</v>
+        <v>34.49588775634766</v>
       </c>
       <c r="C2" t="n">
         <v>57.06753158569336</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.87705993652344</v>
+        <v>35.87707901000977</v>
       </c>
       <c r="C3" t="n">
         <v>59.35245132446289</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76356887817383</v>
+        <v>37.76355361938477</v>
       </c>
       <c r="C4" t="n">
         <v>62.15541076660156</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.51108932495117</v>
+        <v>38.51107788085938</v>
       </c>
       <c r="C5" t="n">
         <v>63.3857536315918</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>36.44838333129883</v>
+        <v>36.44839859008789</v>
       </c>
       <c r="C6" t="n">
         <v>59.99074935913086</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>36.12399673461914</v>
+        <v>36.12398529052734</v>
       </c>
       <c r="C7" t="n">
         <v>59.13043594360352</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>36.129638671875</v>
+        <v>36.12961959838867</v>
       </c>
       <c r="C8" t="n">
         <v>59.13968658447266</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>37.46337890625</v>
+        <v>37.46337509155273</v>
       </c>
       <c r="C9" t="n">
         <v>61.32284927368164</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>37.69815444946289</v>
+        <v>37.69816589355469</v>
       </c>
       <c r="C10" t="n">
         <v>61.39685440063477</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.27153396606445</v>
+        <v>39.27152252197266</v>
       </c>
       <c r="C12" t="n">
         <v>63.95929718017578</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.1086311340332</v>
+        <v>40.10862350463867</v>
       </c>
       <c r="C13" t="n">
         <v>65.01387786865234</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.60829925537109</v>
+        <v>42.6082763671875</v>
       </c>
       <c r="C14" t="n">
         <v>69.06568145751953</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.42669677734375</v>
+        <v>42.42670059204102</v>
       </c>
       <c r="C16" t="n">
         <v>68.41812896728516</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>44.73848342895508</v>
+        <v>44.73848724365234</v>
       </c>
       <c r="C18" t="n">
         <v>72.14616394042969</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>46.3196907043457</v>
+        <v>46.31969833374023</v>
       </c>
       <c r="C19" t="n">
         <v>74.34782409667969</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>49.77768325805664</v>
+        <v>49.77767562866211</v>
       </c>
       <c r="C20" t="n">
         <v>79.89823913574219</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>51.87551879882812</v>
+        <v>51.87549591064453</v>
       </c>
       <c r="C21" t="n">
         <v>83.26549530029297</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>56.56333160400391</v>
+        <v>56.56334686279297</v>
       </c>
       <c r="C22" t="n">
         <v>90.43478393554688</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>56.61538696289062</v>
+        <v>56.61537933349609</v>
       </c>
       <c r="C23" t="n">
         <v>90.51803588867188</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.30393600463867</v>
+        <v>57.30392837524414</v>
       </c>
       <c r="C24" t="n">
         <v>91.61887359619141</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>57.28253936767578</v>
+        <v>57.28254318237305</v>
       </c>
       <c r="C25" t="n">
         <v>91.23959350585938</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>52.07876586914062</v>
+        <v>52.07875061035156</v>
       </c>
       <c r="C26" t="n">
         <v>82.95097351074219</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>53.0428352355957</v>
+        <v>53.04281997680664</v>
       </c>
       <c r="C27" t="n">
         <v>84.48658752441406</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>53.68689346313477</v>
+        <v>53.68692016601562</v>
       </c>
       <c r="C28" t="n">
         <v>85.10638427734375</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>57.43917846679688</v>
+        <v>57.43915939331055</v>
       </c>
       <c r="C29" t="n">
         <v>91.05458068847656</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>59.47577285766602</v>
+        <v>59.47578811645508</v>
       </c>
       <c r="C30" t="n">
         <v>94.28307342529297</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>57.94895935058594</v>
+        <v>57.94895553588867</v>
       </c>
       <c r="C31" t="n">
         <v>91.45236206054688</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>55.8094367980957</v>
+        <v>55.80942535400391</v>
       </c>
       <c r="C32" t="n">
         <v>88.07585906982422</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>53.83989715576172</v>
+        <v>53.83988952636719</v>
       </c>
       <c r="C33" t="n">
         <v>84.96762084960938</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>40.39574813842773</v>
+        <v>40.39573287963867</v>
       </c>
       <c r="C34" t="n">
         <v>63.35800170898438</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>28.16909217834473</v>
+        <v>28.16908073425293</v>
       </c>
       <c r="C36" t="n">
         <v>44.18131256103516</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>29.92421722412109</v>
+        <v>29.92420959472656</v>
       </c>
       <c r="C37" t="n">
         <v>46.50323867797852</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>29.94206809997559</v>
+        <v>29.94207000732422</v>
       </c>
       <c r="C38" t="n">
         <v>46.53099060058594</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>27.53121185302734</v>
+        <v>27.5312328338623</v>
       </c>
       <c r="C39" t="n">
         <v>42.78445816040039</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.74229431152344</v>
+        <v>33.74229049682617</v>
       </c>
       <c r="C40" t="n">
         <v>52.03515243530273</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>39.53095245361328</v>
+        <v>39.53096008300781</v>
       </c>
       <c r="C41" t="n">
         <v>60.96207046508789</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>39.01444625854492</v>
+        <v>39.01446151733398</v>
       </c>
       <c r="C43" t="n">
         <v>59.7502326965332</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>45.06080627441406</v>
+        <v>45.06082153320312</v>
       </c>
       <c r="C44" t="n">
         <v>69.01017761230469</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>45.32054901123047</v>
+        <v>45.32055282592773</v>
       </c>
       <c r="C45" t="n">
         <v>69.407958984375</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>47.13081359863281</v>
+        <v>47.13080215454102</v>
       </c>
       <c r="C46" t="n">
         <v>71.76688385009766</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>50.38098907470703</v>
+        <v>50.38097381591797</v>
       </c>
       <c r="C48" t="n">
         <v>76.71600341796875</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>49.51443099975586</v>
+        <v>49.51443481445312</v>
       </c>
       <c r="C49" t="n">
         <v>74.98612213134766</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.89119720458984</v>
+        <v>41.89119338989258</v>
       </c>
       <c r="C51" t="n">
         <v>63.44125747680664</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>45.47126388549805</v>
+        <v>45.47127532958984</v>
       </c>
       <c r="C52" t="n">
         <v>68.40888214111328</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>47.21140289306641</v>
+        <v>47.2114143371582</v>
       </c>
       <c r="C53" t="n">
         <v>71.02682495117188</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.14129257202148</v>
+        <v>40.14130020141602</v>
       </c>
       <c r="C55" t="n">
         <v>59.9537467956543</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>44.95379257202148</v>
+        <v>44.95381164550781</v>
       </c>
       <c r="C56" t="n">
         <v>67.14153289794922</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>45.85188293457031</v>
+        <v>45.85189056396484</v>
       </c>
       <c r="C57" t="n">
         <v>68.48288726806641</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>52.93669509887695</v>
+        <v>52.93669128417969</v>
       </c>
       <c r="C59" t="n">
         <v>78.60314178466797</v>
@@ -1725,7 +1725,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>56.96817016601562</v>
+        <v>56.96816253662109</v>
       </c>
       <c r="C61" t="n">
         <v>84.13506317138672</v>
@@ -1754,7 +1754,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>54.65060424804688</v>
+        <v>54.65059280395508</v>
       </c>
       <c r="C62" t="n">
         <v>80.71230316162109</v>
@@ -1783,7 +1783,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>57.62583160400391</v>
+        <v>57.62584686279297</v>
       </c>
       <c r="C63" t="n">
         <v>85.10638427734375</v>
@@ -1812,7 +1812,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>56.85111618041992</v>
+        <v>56.85108184814453</v>
       </c>
       <c r="C64" t="n">
         <v>83.42276000976562</v>
@@ -1841,7 +1841,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>60.21749877929688</v>
+        <v>60.21752548217773</v>
       </c>
       <c r="C65" t="n">
         <v>88.36262512207031</v>
@@ -1870,7 +1870,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>59.94644546508789</v>
+        <v>59.94644165039062</v>
       </c>
       <c r="C66" t="n">
         <v>87.96484375</v>
@@ -1899,7 +1899,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>60.62609481811523</v>
+        <v>60.62610626220703</v>
       </c>
       <c r="C67" t="n">
         <v>88.41812896728516</v>
@@ -1928,7 +1928,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.28118896484375</v>
+        <v>56.28117370605469</v>
       </c>
       <c r="C68" t="n">
         <v>82.08140563964844</v>
@@ -1957,7 +1957,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>51.92989349365234</v>
+        <v>51.92990112304688</v>
       </c>
       <c r="C69" t="n">
         <v>75.73542785644531</v>
@@ -1986,7 +1986,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>48.799560546875</v>
+        <v>48.79956436157227</v>
       </c>
       <c r="C70" t="n">
         <v>70.64755249023438</v>
@@ -2015,7 +2015,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>55.04245758056641</v>
+        <v>55.04244995117188</v>
       </c>
       <c r="C71" t="n">
         <v>79.68547821044922</v>
@@ -2044,7 +2044,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>53.5152702331543</v>
+        <v>53.51529312133789</v>
       </c>
       <c r="C72" t="n">
         <v>77.47456359863281</v>
@@ -2073,7 +2073,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>54.80949783325195</v>
+        <v>54.80952453613281</v>
       </c>
       <c r="C73" t="n">
         <v>78.80666351318359</v>
@@ -2102,7 +2102,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>56.6367073059082</v>
+        <v>56.63670349121094</v>
       </c>
       <c r="C74" t="n">
         <v>81.43386077880859</v>
@@ -2131,7 +2131,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>58.05860137939453</v>
+        <v>58.05857467651367</v>
       </c>
       <c r="C75" t="n">
         <v>83.47826385498047</v>
@@ -2160,7 +2160,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>59.47995758056641</v>
+        <v>59.47996139526367</v>
       </c>
       <c r="C76" t="n">
         <v>84.92137145996094</v>
@@ -2189,7 +2189,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>55.39152145385742</v>
+        <v>55.39151763916016</v>
       </c>
       <c r="C77" t="n">
         <v>79.08418273925781</v>
@@ -2218,7 +2218,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>51.21237182617188</v>
+        <v>51.21238327026367</v>
       </c>
       <c r="C78" t="n">
         <v>73.11748504638672</v>
@@ -2247,7 +2247,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>52.74463653564453</v>
+        <v>52.74465179443359</v>
       </c>
       <c r="C79" t="n">
         <v>74.68085479736328</v>
@@ -2276,7 +2276,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>52.54864883422852</v>
+        <v>52.54862213134766</v>
       </c>
       <c r="C80" t="n">
         <v>74.40332794189453</v>
@@ -2305,7 +2305,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>53.95335006713867</v>
+        <v>53.95331954956055</v>
       </c>
       <c r="C81" t="n">
         <v>76.39222717285156</v>
@@ -2334,7 +2334,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>54.45068359375</v>
+        <v>54.45069885253906</v>
       </c>
       <c r="C82" t="n">
         <v>76.50323486328125</v>
@@ -2363,7 +2363,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>51.04670333862305</v>
+        <v>51.04670715332031</v>
       </c>
       <c r="C83" t="n">
         <v>71.72062683105469</v>
@@ -2392,7 +2392,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>54.60869598388672</v>
+        <v>54.60871505737305</v>
       </c>
       <c r="C84" t="n">
         <v>76.72525024414062</v>
@@ -2421,7 +2421,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>55.740478515625</v>
+        <v>55.74046325683594</v>
       </c>
       <c r="C85" t="n">
         <v>77.72432708740234</v>
@@ -2450,7 +2450,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>58.00272369384766</v>
+        <v>58.00274276733398</v>
       </c>
       <c r="C86" t="n">
         <v>80.87881469726562</v>
@@ -2479,7 +2479,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.27962112426758</v>
+        <v>57.27961349487305</v>
       </c>
       <c r="C87" t="n">
         <v>79.87049102783203</v>
@@ -2566,7 +2566,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>63.14330291748047</v>
+        <v>63.1432991027832</v>
       </c>
       <c r="C90" t="n">
         <v>87.33580017089844</v>
@@ -2595,7 +2595,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.69956207275391</v>
+        <v>61.6995735168457</v>
       </c>
       <c r="C91" t="n">
         <v>84.70860290527344</v>
@@ -2624,7 +2624,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>73.20127868652344</v>
+        <v>73.20126342773438</v>
       </c>
       <c r="C92" t="n">
         <v>100.4995346069336</v>
@@ -2653,7 +2653,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>68.82157897949219</v>
+        <v>68.82160949707031</v>
       </c>
       <c r="C93" t="n">
         <v>94.48658752441406</v>
@@ -2682,7 +2682,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>72.27394104003906</v>
+        <v>72.27394866943359</v>
       </c>
       <c r="C94" t="n">
         <v>98.58464050292969</v>
@@ -2711,7 +2711,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>73.92869567871094</v>
+        <v>73.92872619628906</v>
       </c>
       <c r="C95" t="n">
         <v>100.8418121337891</v>
@@ -2740,7 +2740,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>73.80663299560547</v>
+        <v>73.80662536621094</v>
       </c>
       <c r="C96" t="n">
         <v>100.6753005981445</v>
@@ -2798,7 +2798,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>71.75327301025391</v>
+        <v>71.75328063964844</v>
       </c>
       <c r="C98" t="n">
         <v>97.26179504394531</v>
@@ -2827,7 +2827,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>82.79538726806641</v>
+        <v>82.79540252685547</v>
       </c>
       <c r="C99" t="n">
         <v>112.2294158935547</v>
@@ -2856,7 +2856,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>81.77101898193359</v>
+        <v>81.77100372314453</v>
       </c>
       <c r="C100" t="n">
         <v>110.1202621459961</v>
@@ -2885,7 +2885,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>80.72688293457031</v>
+        <v>80.72687530517578</v>
       </c>
       <c r="C101" t="n">
         <v>108.7141571044922</v>
@@ -2914,7 +2914,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>82.40983581542969</v>
+        <v>82.40981292724609</v>
       </c>
       <c r="C102" t="n">
         <v>110.9805755615234</v>
@@ -2943,7 +2943,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>88.8829345703125</v>
+        <v>88.88295745849609</v>
       </c>
       <c r="C103" t="n">
         <v>118.982421875</v>
@@ -2972,7 +2972,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>91.18415832519531</v>
+        <v>91.18412780761719</v>
       </c>
       <c r="C104" t="n">
         <v>122.0629043579102</v>
@@ -3030,7 +3030,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>90.47791290283203</v>
+        <v>90.47792053222656</v>
       </c>
       <c r="C106" t="n">
         <v>120.4255294799805</v>
@@ -3088,7 +3088,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>99.96495819091797</v>
+        <v>99.96497344970703</v>
       </c>
       <c r="C108" t="n">
         <v>133.052734375</v>
@@ -3117,7 +3117,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>100.7660293579102</v>
+        <v>100.7660217285156</v>
       </c>
       <c r="C109" t="n">
         <v>133.4227600097656</v>
@@ -3146,7 +3146,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>101.7301788330078</v>
+        <v>101.7301940917969</v>
       </c>
       <c r="C110" t="n">
         <v>134.6993560791016</v>
@@ -3175,7 +3175,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>109.0869674682617</v>
+        <v>109.0869445800781</v>
       </c>
       <c r="C111" t="n">
         <v>144.4403381347656</v>
@@ -3233,7 +3233,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>100.7413101196289</v>
+        <v>100.7413177490234</v>
       </c>
       <c r="C113" t="n">
         <v>132.6826934814453</v>
@@ -3262,7 +3262,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>103.0802307128906</v>
+        <v>103.080207824707</v>
       </c>
       <c r="C114" t="n">
         <v>135.76318359375</v>
@@ -3349,7 +3349,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>98.56400299072266</v>
+        <v>98.56398773193359</v>
       </c>
       <c r="C117" t="n">
         <v>129.0749359130859</v>
@@ -3378,7 +3378,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>90.70913696289062</v>
+        <v>90.70912933349609</v>
       </c>
       <c r="C118" t="n">
         <v>118.0203552246094</v>
@@ -3407,7 +3407,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>98.81451416015625</v>
+        <v>98.81449890136719</v>
       </c>
       <c r="C119" t="n">
         <v>128.5661468505859</v>
@@ -3465,7 +3465,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>93.07391357421875</v>
+        <v>93.07395172119141</v>
       </c>
       <c r="C121" t="n">
         <v>120.3607788085938</v>
@@ -3494,7 +3494,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>90.64179229736328</v>
+        <v>90.64177703857422</v>
       </c>
       <c r="C122" t="n">
         <v>117.2155380249023</v>
@@ -3552,7 +3552,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>103.6605453491211</v>
+        <v>103.6605834960938</v>
       </c>
       <c r="C124" t="n">
         <v>133.2562408447266</v>
@@ -3639,7 +3639,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>102.8611679077148</v>
+        <v>102.8611907958984</v>
       </c>
       <c r="C127" t="n">
         <v>131.3968505859375</v>
@@ -3668,7 +3668,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>108.2055435180664</v>
+        <v>108.2055282592773</v>
       </c>
       <c r="C128" t="n">
         <v>138.2238616943359</v>
@@ -3726,7 +3726,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>108.8717956542969</v>
+        <v>108.8718109130859</v>
       </c>
       <c r="C130" t="n">
         <v>139.0749359130859</v>
@@ -3755,7 +3755,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>105.1048126220703</v>
+        <v>105.1048355102539</v>
       </c>
       <c r="C131" t="n">
         <v>133.4199981689453</v>
@@ -3784,7 +3784,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>113.801872253418</v>
+        <v>113.8018493652344</v>
       </c>
       <c r="C132" t="n">
         <v>144.4600067138672</v>
@@ -3813,7 +3813,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>113.9730987548828</v>
+        <v>113.9731140136719</v>
       </c>
       <c r="C133" t="n">
         <v>143.8200073242188</v>
@@ -3842,7 +3842,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>110.7556457519531</v>
+        <v>110.7556762695312</v>
       </c>
       <c r="C134" t="n">
         <v>139.7599945068359</v>
@@ -3871,7 +3871,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>111.3183670043945</v>
+        <v>111.3183517456055</v>
       </c>
       <c r="C135" t="n">
         <v>140.4700012207031</v>
@@ -3958,7 +3958,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>114.9617691040039</v>
+        <v>114.961784362793</v>
       </c>
       <c r="C138" t="n">
         <v>144.0599975585938</v>
@@ -3987,7 +3987,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>114.9174499511719</v>
+        <v>114.9174728393555</v>
       </c>
       <c r="C139" t="n">
         <v>143.0599975585938</v>
@@ -4016,7 +4016,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>114.1865005493164</v>
+        <v>114.1864700317383</v>
       </c>
       <c r="C140" t="n">
         <v>142.1499938964844</v>
@@ -4045,7 +4045,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>116.7730560302734</v>
+        <v>116.7730941772461</v>
       </c>
       <c r="C141" t="n">
         <v>145.3699951171875</v>
@@ -4074,7 +4074,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>121.4722900390625</v>
+        <v>121.4722595214844</v>
       </c>
       <c r="C142" t="n">
         <v>151.2200012207031</v>
@@ -4103,7 +4103,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>128.8657379150391</v>
+        <v>128.8657531738281</v>
       </c>
       <c r="C143" t="n">
         <v>159.4299926757812</v>
@@ -4132,7 +4132,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>131.7836303710938</v>
+        <v>131.7836456298828</v>
       </c>
       <c r="C144" t="n">
         <v>163.0399932861328</v>
@@ -4161,7 +4161,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>133.3940734863281</v>
+        <v>133.3940582275391</v>
       </c>
       <c r="C145" t="n">
         <v>164.0800018310547</v>
@@ -4190,7 +4190,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>136.8817901611328</v>
+        <v>136.8817749023438</v>
       </c>
       <c r="C146" t="n">
         <v>168.3699951171875</v>
@@ -4219,7 +4219,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>130.7193450927734</v>
+        <v>130.7193756103516</v>
       </c>
       <c r="C147" t="n">
         <v>160.7899932861328</v>
@@ -4248,7 +4248,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>130.1938781738281</v>
+        <v>130.19384765625</v>
       </c>
       <c r="C148" t="n">
         <v>159.0299987792969</v>
@@ -4277,7 +4277,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>132.8628082275391</v>
+        <v>132.8627777099609</v>
       </c>
       <c r="C149" t="n">
         <v>162.2899932861328</v>
@@ -4306,7 +4306,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>132.1423187255859</v>
+        <v>132.1423492431641</v>
       </c>
       <c r="C150" t="n">
         <v>161.4100036621094</v>
@@ -4335,7 +4335,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>128.3974914550781</v>
+        <v>128.3974456787109</v>
       </c>
       <c r="C151" t="n">
         <v>155.7299957275391</v>
@@ -4364,7 +4364,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>135.3561553955078</v>
+        <v>135.3561401367188</v>
       </c>
       <c r="C152" t="n">
         <v>164.1699981689453</v>
@@ -4393,7 +4393,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>137.1040344238281</v>
+        <v>137.1040496826172</v>
       </c>
       <c r="C153" t="n">
         <v>166.2899932861328</v>
@@ -4422,7 +4422,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>138.6355895996094</v>
+        <v>138.6355743408203</v>
       </c>
       <c r="C154" t="n">
         <v>167.0500030517578</v>
@@ -4480,7 +4480,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>133.5067596435547</v>
+        <v>133.5068054199219</v>
       </c>
       <c r="C156" t="n">
         <v>160.8699951171875</v>
@@ -4538,7 +4538,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>137.3683929443359</v>
+        <v>137.3683471679688</v>
       </c>
       <c r="C158" t="n">
         <v>164.3899993896484</v>
@@ -4567,7 +4567,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>151.3984985351562</v>
+        <v>151.3984680175781</v>
       </c>
       <c r="C159" t="n">
         <v>181.1799926757812</v>
@@ -4625,7 +4625,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>173.0186004638672</v>
+        <v>173.0185852050781</v>
       </c>
       <c r="C161" t="n">
         <v>205.7899932861328</v>
@@ -4654,7 +4654,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>171.1689605712891</v>
+        <v>171.1688842773438</v>
       </c>
       <c r="C162" t="n">
         <v>203.5899963378906</v>
@@ -4683,7 +4683,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>191.3142547607422</v>
+        <v>191.3142242431641</v>
       </c>
       <c r="C163" t="n">
         <v>226.3699951171875</v>
@@ -4712,7 +4712,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>192.9199981689453</v>
+        <v>192.9200134277344</v>
       </c>
       <c r="C164" t="n">
         <v>228.2700042724609</v>
@@ -4741,7 +4741,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>190.9339141845703</v>
+        <v>190.9339294433594</v>
       </c>
       <c r="C165" t="n">
         <v>225.9199981689453</v>
@@ -4770,7 +4770,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>188.4917755126953</v>
+        <v>188.4917297363281</v>
       </c>
       <c r="C166" t="n">
         <v>221.8600006103516</v>
@@ -4828,7 +4828,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>200.7854614257812</v>
+        <v>200.7854461669922</v>
       </c>
       <c r="C168" t="n">
         <v>236.3300018310547</v>
@@ -4857,7 +4857,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>200.635986328125</v>
+        <v>200.6359710693359</v>
       </c>
       <c r="C169" t="n">
         <v>234.9900054931641</v>
@@ -4915,7 +4915,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>187.5044250488281</v>
+        <v>187.5044708251953</v>
       </c>
       <c r="C171" t="n">
         <v>219.6100006103516</v>
@@ -4944,7 +4944,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>171.541259765625</v>
+        <v>171.5412750244141</v>
       </c>
       <c r="C172" t="n">
         <v>199.6100006103516</v>
@@ -4973,7 +4973,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>193.8594818115234</v>
+        <v>193.8594207763672</v>
       </c>
       <c r="C173" t="n">
         <v>225.5800018310547</v>
@@ -5031,7 +5031,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>208.6783142089844</v>
+        <v>208.6783447265625</v>
       </c>
       <c r="C175" t="n">
         <v>241.4600067138672</v>
@@ -5060,7 +5060,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>247.7158966064453</v>
+        <v>247.7158813476562</v>
       </c>
       <c r="C176" t="n">
         <v>286.6300048828125</v>
@@ -5089,7 +5089,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>252.5815124511719</v>
+        <v>252.5815277099609</v>
       </c>
       <c r="C177" t="n">
         <v>292.260009765625</v>
@@ -5118,7 +5118,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>258.6004638671875</v>
+        <v>258.6004333496094</v>
       </c>
       <c r="C178" t="n">
         <v>297.8599853515625</v>
@@ -5176,7 +5176,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>243.2160186767578</v>
+        <v>243.2160339355469</v>
       </c>
       <c r="C180" t="n">
         <v>280.1400146484375</v>
@@ -5263,7 +5263,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>223.0302734375</v>
+        <v>223.0302886962891</v>
       </c>
       <c r="C183" t="n">
         <v>255.6199951171875</v>
@@ -5292,7 +5292,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>246.7809753417969</v>
+        <v>246.781005859375</v>
       </c>
       <c r="C184" t="n">
         <v>281.3399963378906</v>
@@ -5321,7 +5321,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>253.0439147949219</v>
+        <v>253.0439910888672</v>
       </c>
       <c r="C185" t="n">
         <v>288.4800109863281</v>
@@ -5350,7 +5350,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>262.8505554199219</v>
+        <v>262.8506469726562</v>
       </c>
       <c r="C186" t="n">
         <v>299.6600036621094</v>
@@ -5379,7 +5379,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>253.6620483398438</v>
+        <v>253.6619720458984</v>
       </c>
       <c r="C187" t="n">
         <v>287.6799926757812</v>
@@ -5408,7 +5408,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>256.6159362792969</v>
+        <v>256.6159057617188</v>
       </c>
       <c r="C188" t="n">
         <v>291.0299987792969</v>
@@ -5437,7 +5437,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>237.6407012939453</v>
+        <v>237.6406707763672</v>
       </c>
       <c r="C189" t="n">
         <v>269.510009765625</v>
@@ -5466,7 +5466,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>227.1344451904297</v>
+        <v>227.1344604492188</v>
       </c>
       <c r="C190" t="n">
         <v>256.1099853515625</v>
@@ -5495,7 +5495,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>265.890380859375</v>
+        <v>265.8903198242188</v>
       </c>
       <c r="C191" t="n">
         <v>299.8099975585938</v>
@@ -5582,7 +5582,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>251.44287109375</v>
+        <v>251.4429168701172</v>
       </c>
       <c r="C194" t="n">
         <v>282.1199951171875</v>
@@ -5640,7 +5640,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>224.1698303222656</v>
+        <v>224.1698150634766</v>
       </c>
       <c r="C196" t="n">
         <v>249.9100036621094</v>
@@ -5669,7 +5669,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>209.9613189697266</v>
+        <v>209.9613342285156</v>
       </c>
       <c r="C197" t="n">
         <v>234.0700073242188</v>
@@ -5698,7 +5698,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>220.8060607910156</v>
+        <v>220.8060760498047</v>
       </c>
       <c r="C198" t="n">
         <v>246.1600036621094</v>
@@ -5756,7 +5756,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>224.1564331054688</v>
+        <v>224.1564178466797</v>
       </c>
       <c r="C200" t="n">
         <v>248.2299957275391</v>
@@ -5785,7 +5785,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>227.9671783447266</v>
+        <v>227.9671478271484</v>
       </c>
       <c r="C201" t="n">
         <v>252.4499969482422</v>
@@ -5814,7 +5814,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>211.6389770507812</v>
+        <v>211.6390075683594</v>
       </c>
       <c r="C202" t="n">
         <v>232.7299957275391</v>
@@ -5901,7 +5901,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>281.7900390625</v>
+        <v>281.7900695800781</v>
       </c>
       <c r="C205" t="n">
         <v>308.260009765625</v>
@@ -5930,7 +5930,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>292.9881591796875</v>
+        <v>292.9881286621094</v>
       </c>
       <c r="C206" t="n">
         <v>320.510009765625</v>
@@ -5988,7 +5988,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>264.2004699707031</v>
+        <v>264.2005310058594</v>
       </c>
       <c r="C208" t="n">
         <v>287.2099914550781</v>
@@ -6017,7 +6017,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>270.7777099609375</v>
+        <v>270.7776794433594</v>
       </c>
       <c r="C209" t="n">
         <v>294.3599853515625</v>
@@ -6046,7 +6046,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>247.5782165527344</v>
+        <v>247.5782012939453</v>
       </c>
       <c r="C210" t="n">
         <v>269.1400146484375</v>
@@ -6220,7 +6220,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>251.8983001708984</v>
+        <v>251.8983154296875</v>
       </c>
       <c r="C216" t="n">
         <v>270.5499877929688</v>
@@ -6278,7 +6278,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>239.6104583740234</v>
+        <v>239.6104431152344</v>
       </c>
       <c r="C218" t="n">
         <v>255.7100067138672</v>
@@ -6307,7 +6307,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>219.3047790527344</v>
+        <v>219.3047943115234</v>
       </c>
       <c r="C219" t="n">
         <v>234.0399932861328</v>
@@ -6336,7 +6336,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>228.681640625</v>
+        <v>228.6816558837891</v>
       </c>
       <c r="C220" t="n">
         <v>242.2700042724609</v>
@@ -6365,7 +6365,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>223.0842590332031</v>
+        <v>223.0842742919922</v>
       </c>
       <c r="C221" t="n">
         <v>236.3399963378906</v>
@@ -6394,7 +6394,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>251.7414703369141</v>
+        <v>251.7414398193359</v>
       </c>
       <c r="C222" t="n">
         <v>266.7000122070312</v>
@@ -6452,7 +6452,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>250.7713470458984</v>
+        <v>250.7713775634766</v>
       </c>
       <c r="C224" t="n">
         <v>263.8500061035156</v>
@@ -6539,7 +6539,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>296.9025268554688</v>
+        <v>296.9025573730469</v>
       </c>
       <c r="C227" t="n">
         <v>310.5299987792969</v>
@@ -6568,7 +6568,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>319.6580810546875</v>
+        <v>319.6580505371094</v>
       </c>
       <c r="C228" t="n">
         <v>334.3299865722656</v>
@@ -6655,7 +6655,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>304.1318664550781</v>
+        <v>304.1318969726562</v>
       </c>
       <c r="C231" t="n">
         <v>316.1499938964844</v>
@@ -6800,7 +6800,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>280.4071960449219</v>
+        <v>280.4071655273438</v>
       </c>
       <c r="C236" t="n">
         <v>287.8800048828125</v>
@@ -6858,7 +6858,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>265.6406555175781</v>
+        <v>265.6407165527344</v>
       </c>
       <c r="C238" t="n">
         <v>272.7200012207031</v>
